--- a/config/universe-generated/templates/UniverseBindings.xlsx
+++ b/config/universe-generated/templates/UniverseBindings.xlsx
@@ -45,16 +45,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>1520e7821566a309</t>
+    <t>e06db9c2a6304f97</t>
   </si>
   <si>
     <t>#name</t>
@@ -90,7 +90,7 @@
     <t>bool</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
@@ -114,7 +114,7 @@
     <t>list</t>
   </si>
   <si>
-    <t>f497803f34dcf351</t>
+    <t>972a6626ea8d0431</t>
   </si>
   <si>
     <t>pool_id</t>
@@ -150,7 +150,7 @@
     <t>UniverseEncounterGroup</t>
   </si>
   <si>
-    <t>571984338420f544</t>
+    <t>148c38fc9c7d9c74</t>
   </si>
   <si>
     <t>source_group_id</t>
@@ -189,7 +189,7 @@
     <t>UniverseEncounterMember</t>
   </si>
   <si>
-    <t>766b31b8036f726c</t>
+    <t>416f393e4f067488</t>
   </si>
   <si>
     <t>group_id</t>
@@ -237,7 +237,7 @@
     <t>UniverseEncounterWave</t>
   </si>
   <si>
-    <t>8f77e125b36f4f92</t>
+    <t>d94ec093e890688e</t>
   </si>
   <si>
     <t>member_id</t>
@@ -252,7 +252,7 @@
     <t>UniverseEncounterWaveEnemy</t>
   </si>
   <si>
-    <t>0c7ec3730b10fff7</t>
+    <t>bab57c4869a7945f</t>
   </si>
   <si>
     <t>wave_id</t>
@@ -276,7 +276,7 @@
     <t>UniverseEncounterPool</t>
   </si>
   <si>
-    <t>a22b7cefcea09ab8</t>
+    <t>db48be4dff32cacc</t>
   </si>
   <si>
     <t>room_id</t>
@@ -306,7 +306,7 @@
     <t>UniverseEncounterPoolGroup</t>
   </si>
   <si>
-    <t>9247a01d952a7f19</t>
+    <t>29c74a5cc35e110b</t>
   </si>
   <si>
     <t>condition_key</t>
@@ -318,7 +318,7 @@
     <t>UniverseEncounterPoolFixed</t>
   </si>
   <si>
-    <t>2b08b493238e08d3</t>
+    <t>70bfbe994645c167</t>
   </si>
   <si>
     <t>source_content_id</t>
@@ -327,7 +327,7 @@
     <t>UniverseMechanicRule</t>
   </si>
   <si>
-    <t>a9046b0aa5a2ae4e</t>
+    <t>bd45be4e17a105cc</t>
   </si>
   <si>
     <t>source_record_stable_key</t>
@@ -366,7 +366,7 @@
     <t>UniverseActivityBinding</t>
   </si>
   <si>
-    <t>b2c0f60eb215b1a3</t>
+    <t>f8cf1b2e4df911e1</t>
   </si>
   <si>
     <t>profile_id</t>
@@ -399,7 +399,7 @@
     <t>UniverseActivityDomainBinding</t>
   </si>
   <si>
-    <t>3b82bb1fc113aa2f</t>
+    <t>e65b6fb8e129f5a1</t>
   </si>
   <si>
     <t>activity_binding_id</t>
